--- a/Employee_Reports_wi52/Regin Alis Q0187.xlsx
+++ b/Employee_Reports_wi52/Regin Alis Q0187.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -704,11 +713,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +762,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-317</v>
+        <v>-325</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -790,11 +799,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -839,11 +848,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -888,11 +897,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -937,11 +946,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -986,11 +995,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1035,11 +1044,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-33</v>
+        <v>-41</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1050,41 +1059,41 @@
       <c r="K13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1121,11 +1130,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1167,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1195,11 +1204,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1232,11 +1241,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1269,11 +1278,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1456,7 +1465,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7991</v>
+        <v>7983</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1551,7 +1560,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1580,7 +1589,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1609,7 +1618,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1647,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7984</v>
+        <v>7976</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1667,7 +1676,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7977</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1696,7 +1705,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1734,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1754,7 +1763,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1783,7 +1792,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1812,7 +1821,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1850,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1870,7 +1879,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1899,7 +1908,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1928,7 +1937,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1957,7 +1966,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1986,7 +1995,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2015,7 +2024,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2044,7 +2053,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
